--- a/光伏配储项目/电价数据/2026/兰花站.xlsx
+++ b/光伏配储项目/电价数据/2026/兰花站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.34682</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8504700000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26648</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07955</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.48035</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17738</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27761</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25862</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26315</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24791</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.26204</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.63297</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6115499999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5938</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.76295</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.20482</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.64312</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44087</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6831699999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9434600000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.26969</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.39954</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.1506</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.19283</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.38356</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.50193</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.48649</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.75048</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.80702</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.27123</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.07147</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.94096</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.83325</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.53451</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.50282</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.48444</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42892</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43988</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.74993</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9326100000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.00547</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5372899999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.52786</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5279299999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50843</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48836</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.24781</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39601</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.47781</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.50249</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.51018</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.69478</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6605</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.8719</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.69123</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.75363</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.53761</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.44581</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.68598</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.41161</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62621</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8059400000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8661799999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.24552</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.68786</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.19749</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.9084800000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.29384</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.18095</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.36421</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.09871</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.16556</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.69831</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.05005</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.04501</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.92108</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.14942</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.94657</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45816</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.90178</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.94472</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45696</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3358</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52806</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50548</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.51036</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.46027</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.44293</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.46078</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40724</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45408</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.45265</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.13336</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.17287</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27016</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.09073000000000001</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.90097</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.72458</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.71051</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.9091699999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.90364</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.89079</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.8926900000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.32743</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.8855499999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.8760399999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.87376</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.03188</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.55538</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.61736</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.82538</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.83363</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.7020700000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.74556</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.53465</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.8705499999999999</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.45517</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45632</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51711</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5265599999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.60265</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.6501699999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6547799999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.66484</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.34861</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63459</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69775</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47324</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5098199999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6476799999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.80243</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.78716</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.92592</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.46969</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6617499999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5401900000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.63647</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.82387</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5885199999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.95084</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.75846</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.62809</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5771900000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71757</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34336</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.54027</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5186900000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45642</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46707</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42372</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44434</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.4392200000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.65123</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.46391</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7125900000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42645</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6442899999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.5525</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.46126</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.43404</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.50986</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.68741</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.48202</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.53301</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47675</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40444</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.59727</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.7052</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.51575</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6572100000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55255</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.52267</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50269</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47307</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33816</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14235</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02096</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.27683</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26358</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24972</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.11625</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.08084999999999999</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.45139</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42099</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31419</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.22244</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.23141</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.22703</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.17881</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.15187</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.23918</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24089</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.20408</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18107</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.16085</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24111</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26345</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.18855</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09942000000000001</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04152</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009689999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20557</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04895</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19983</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00654</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05972</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05792</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.314</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.37205</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43596</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7866000000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8702300000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.64764</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5699</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45865</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44304</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5651499999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6116699999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.91776</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.48416</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.27795</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.42708</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.60699</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86278</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26277</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6203</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.4669700000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25812</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25592</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27711</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32084</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91316</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.5298099999999999</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.21637</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.41765</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.22256</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.28366</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.46269</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.30903</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.24001</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.91253</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.68426</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.27582</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7583099999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.89471</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.7069099999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.2248</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.22895</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.48378</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.54343</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.49968</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.44778</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.46235</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.43393</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.28763</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.28293</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48604</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.16796</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.42181</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.26912</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15733</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28401</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.009990000000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.27867</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.45834</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.59373</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27184</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.27393</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.25937</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.16038</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.18509</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.17439</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.17845</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.17177</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.14663</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.23985</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.25979</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.15478</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.15336</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.19424</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.16892</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.19165</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.17391</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.24998</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.15221</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.15021</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.21135</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.43716</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26673</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28613</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28617</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.28768</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28767</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.27754</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28005</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24032</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27519</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.28891</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28384</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.47615</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28301</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.46287</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.27907</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3005</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.28636</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.28884</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.21158</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42743</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.71454</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.51383</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48182</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5222100000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.44413</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5869500000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27548</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.42205</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25403</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7509</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.47743</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.44684</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.57331</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.43085</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.42242</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.46185</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.44931</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.68248</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47981</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.43615</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.49373</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.45197</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71951</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.24195</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48041</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22959</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.19866</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27303</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27335</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.18433</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.17714</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26913</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27062</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26914</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.17879</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.17628</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.17601</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.18184</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.2149</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.18777</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.14881</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.14091</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20368</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.22915</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28542</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.28401</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.27078</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.27827</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.23215</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.24269</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.27756</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.27512</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22194</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.26822</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.20853</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22314</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31689</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27399</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28323</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.26744</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27469</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.27754</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28386</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27453</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.26833</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.27955</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26668</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6393300000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.52538</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.18805</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29201</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.27555</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48675</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6732899999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.62903</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6771699999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.45586</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.30975</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.26661</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.27136</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.29151</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44432</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45993</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.49896</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.54215</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.56877</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67625</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.84766</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.5555599999999999</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.43007</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.27124</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76563</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60884</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6397999999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.30188</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.27672</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.03736</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.26689</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.27679</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.26561</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27307</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28455</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.46615</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4109</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42925</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.44173</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.22139</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.21694</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.24071</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.22859</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.17027</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.18538</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.17772</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.2122</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.17881</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.27042</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.26152</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.21735</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.20528</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.04167</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.14878</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.18543</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.14754</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.04126</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.13901</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.14312</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.18151</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.14099</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.14347</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.14596</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.04098</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.14844</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.04101</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.15839</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.16825</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.13214</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27039</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.6293800000000001</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00374</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.40348</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.23888</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.25749</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.26839</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.26292</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.20379</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.23437</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.21549</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.2319</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.26183</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.24766</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.16805</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24766</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.15144</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27353</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.15405</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.23113</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.21945</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27667</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27327</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27618</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26619</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.17049</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.16771</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26121</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.04803</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19066</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21335</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20444</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.00176</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.04576</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.04581</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.04581</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18519</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.04581</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.04582</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.16153</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.03577</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24143</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.00307</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00992</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15779</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02211</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01397</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04327</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00315</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.0358</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01005</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03523</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20835</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28079</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28718</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26074</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.26301</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26596</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26812</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.14896</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.14505</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.14672</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.14309</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.13299</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.04502</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.04475</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.17128</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26775</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.2182</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.24488</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8549800000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86291</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08678</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.04197</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24177</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28288</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.61029</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06979</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47567</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.64012</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.52436</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.79644</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9884299999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.6145700000000001</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83823</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8427100000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94517</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30039</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.47497</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.28636</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.25454</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.16925</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.24932</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24293</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.23682</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.20147</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.23034</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.18644</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.14753</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.18229</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.14253</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.14499</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.13354</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.16099</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.21434</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.26002</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22667</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23499</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24454</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26919</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25874</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.27015</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28486</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5946399999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.44261</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.47046</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48463</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8548600000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.8550800000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5548500000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.70197</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.90308</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.58728</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42037</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19599</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31145</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28669</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.54083</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.55133</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.20102</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.8802300000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.58535</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.77338</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49891</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.6147</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.54389</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.44468</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.74641</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.6880499999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.1446</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8794299999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7518899999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.6115700000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31608</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27767</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27704</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26191</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.53265</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19799</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.49947</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.48574</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42922</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5293600000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.4563</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47766</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.59112</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.49676</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.42113</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.43477</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31968</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.73498</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46759</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.48484</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.44161</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44235</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.46357</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.44061</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5374099999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.43198</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.45273</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33421</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17616</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19875</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14739</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04839</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12207</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22676</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14275</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14593</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18687</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16069</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17037</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20391</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16863</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.43292</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.54388</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.42023</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.44871</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.48662</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.46268</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.44393</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47102</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36577</v>
       </c>
     </row>
   </sheetData>
